--- a/reportes_generados/reporte_entrenamiento.xlsx
+++ b/reportes_generados/reporte_entrenamiento.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generado: 2026-07-08 06:22</t>
+          <t>Generado: 2026-07-09 11:40</t>
         </is>
       </c>
     </row>
